--- a/AAII_Financials/Quarterly/HMC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>HMC</t>
   </si>
@@ -656,505 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>37291300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>36608600</v>
+      </c>
+      <c r="F8" s="3">
         <v>34077800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>35762200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>37014300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>35793700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>35180700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>37642100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>33598500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>35895100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>38238000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>33371200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>31988100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>32980500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>31511100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>27151700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>25811200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>25734500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>25342000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>24545400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>26341400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>25692800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>27645600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>28444200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>18115800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>30465500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>34140600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>34270500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>36605700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>38912000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>37511300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>35689500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>36579400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>35389100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>35772400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>34136800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>33566400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>33381700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>31054500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>28942500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28997800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>33964500</v>
+      </c>
+      <c r="F9" s="3">
         <v>27175600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>28477200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>29592200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>28194400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>27676900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>29615900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>26161400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>28289500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>29908600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>26070000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>25091800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>26559300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>25131000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>21958300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>20652500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>20459000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>20094600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>19577700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>20921200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>20172200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>21557300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>22468400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>15092100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>24329100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>27025300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>27175700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>29005000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>31284800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>29812500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>27913700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>28748900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>27788400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>27689600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>27019200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>25988100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>25976600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>24274800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>22377900</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8293500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2644000</v>
+      </c>
+      <c r="F10" s="3">
         <v>6902200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>7285000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7422000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>7599400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>7503800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>8026200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>7437100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>7605500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8329400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7301300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>6896300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6421200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>6380100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5193400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5158700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5275500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>5247400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4967700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5420300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5520500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>6088300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>5975800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3023700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6136400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>7115300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>7094800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>7600700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>7627200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>7698800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>7775800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>7830500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>7600800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>8082800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>7117600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>7578300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>7405100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>6779700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>6564700</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1196,127 +1220,135 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1496600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3992900</v>
+      </c>
+      <c r="F12" s="3">
         <v>2050600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1968400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2030400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2359100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1702600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1833400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1342000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1932100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1611800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1380800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1369100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2098800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1567300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1273300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1223900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1485300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1406400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1308100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1302600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1686800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1259700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1294800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1389700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1974700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2138500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1611800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1555800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>2223900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1896000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1711600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1730700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>1979900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>1687000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>1554400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>1575400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>1970700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>1563800</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>1130000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1434,16 +1466,22 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>91</v>
+      <c r="E14" s="3">
+        <v>303900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>91</v>
@@ -1475,11 +1513,11 @@
       <c r="O14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1553,53 +1591,59 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1066600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4979900</v>
+      </c>
+      <c r="F15" s="3">
         <v>1126900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1484400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1238000</v>
       </c>
-      <c r="G15" s="3">
-        <v>1301500</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>5249400</v>
+      </c>
+      <c r="J15" s="3">
         <v>1152300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1248600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1168200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1262800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1628800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>1259200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1284300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>6079400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1716,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1712,246 +1762,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>34025900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>42630500</v>
+      </c>
+      <c r="F17" s="3">
         <v>33099600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>34451500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>35321900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>35302500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>32653600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>35841900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>30585400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>33874700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>35543500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>31348500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>29259900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>32628300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>29519600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>25676400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>24313400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>24409300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>23765600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>23110700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>24553900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>24181100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>25609800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>26239900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>19085600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>30515000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>32622400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>32247400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>34293100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>38504900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>35905100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>33697000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>33858000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>34242600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>33199800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>32754200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>31132700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>32156700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>29212300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>26919400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3265400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6022000</v>
+      </c>
+      <c r="F18" s="3">
         <v>978100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1310700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1692400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>491300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2527100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1800200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3013100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2020400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2694400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2022800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2728100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>352200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1991500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1475300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1497700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1325300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1576300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1434700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1787600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1511600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2035800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>2204200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-969800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-49500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1518200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2023000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>2312600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>407100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1606200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1992500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>2721400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>1146500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>2572600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>1382600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>2433700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>1225000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>1842200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>2023100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1993,603 +2057,635 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-275400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1224100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-365700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-99300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-153600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>133500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-313100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>790500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-229400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-252500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>180300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-188100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-668600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>353100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>515600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>353500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>152400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>216200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>402800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>386100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>522400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>336400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>811400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>525600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>359000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>166800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>433800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>675400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>375000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>691100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>574800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>664800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>562300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>608400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>591800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>840300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>620800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>466400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>495300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>404300</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4607300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2266100</v>
+      </c>
+      <c r="F21" s="3">
         <v>2470700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2894400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3084000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1659300</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>5607200</v>
+      </c>
+      <c r="J21" s="3">
         <v>3992600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2258300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4410700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3535600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4142900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3470100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4681000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>6078600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3782100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>3078500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2738200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2557900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3009600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2950600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3422000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3122100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3948700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>3858400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>663800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1616300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3790600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>4149400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>4244900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>3052000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>3749100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>4194300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>4981900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>3398900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>4786300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>3794400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>4663400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>3308600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>3791300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>3855600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>254100</v>
+      </c>
+      <c r="F22" s="3">
         <v>88100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>104400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>96400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>112600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>83000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>89200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>76000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>182400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>86100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>72700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>62500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>82000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>67900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>52500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>50100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>47800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>22300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>25300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>21500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>37700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>14800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>36700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>15600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>84300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>68600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>36800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>32900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>30300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>38800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>27800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>26900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>33200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>28400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>29800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>25800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>32700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>23000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3722200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7390300</v>
+      </c>
+      <c r="F23" s="3">
         <v>1558600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1588500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2026200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>614900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3076000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1273700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3477900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2498200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2732900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2439400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3561400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>151900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2439200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1776400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1600100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1493700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1956900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1795500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2288500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1810400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2832500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>2693100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-626400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>33000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1883300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2661600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>2654700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>1067900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2142200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2629500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>3256800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>1721600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>3135900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>2193100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>3028600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>1658600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>2314500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>2399900</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>807200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-1904700</v>
+      </c>
+      <c r="F24" s="3">
         <v>470800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>684700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>536700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>330400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>954200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>488300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>902300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>793100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>812100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>625200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>912800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-475800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>556700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>467400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>497600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>534200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>530600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>563500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>541300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>225500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>638400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>725800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>55800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>222700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>683600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>730200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>918000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>1111400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>397000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>500000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>832300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>621300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-2195600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>460700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>990000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>671300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>660400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>699200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2707,246 +2803,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2915000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5485600</v>
+      </c>
+      <c r="F26" s="3">
         <v>1087800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>903900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1489500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>284500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2121700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>785400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2575600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1705100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1920800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1814200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2648600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>627600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1882500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1308900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1102500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>959500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1426200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1232100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1747200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1584900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2194100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1967300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-682200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-189600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1199700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1931500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1736700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-43500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1745200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>2129500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>2424500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>1100300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>5331500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>1732500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>2038600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>987300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>1654100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>1700700</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2774100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5593400</v>
+      </c>
+      <c r="F27" s="3">
         <v>979700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>778200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1363200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>204200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1975400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>698200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2453300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1570600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1797000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1695400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2511100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>513400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1737100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1207700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1005700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>829300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1325600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1201900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1635500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1512500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2082100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1876800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-689800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-260300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1060700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1806300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>1578300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-125200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1588200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1958100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>2221000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>974000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>5155100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>1573000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>1874300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>851200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>1497400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>1570800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3064,8 +3178,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3183,8 +3303,14 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3302,8 +3428,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3421,246 +3553,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>275400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1224100</v>
+      </c>
+      <c r="F32" s="3">
         <v>365700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>99300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>153600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-133500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>313100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-790500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>229400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>252500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-180300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>188100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>668600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-353100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-515600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-353500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-152400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-216200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-402800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-386100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-522400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-336400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-811400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-525600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-359000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-166800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-433800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-675400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-375000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-691100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-574800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-664800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-562300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-608400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-591800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-840300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-620800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-466400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-495300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-404300</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>2774100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5593400</v>
+      </c>
+      <c r="F33" s="3">
         <v>979700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>778200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1363200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>204200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1975400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>698200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2453300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1570600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1797000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1695400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2511100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>513400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1737100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1207700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1005700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>829300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1325600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1201900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1635500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1512500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2082100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1876800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-689800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-260300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1060700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1806300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>1578300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-125200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1588200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1958100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>2221000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>974000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>5155100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>1573000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>1874300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>851200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>1497400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>1570800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3778,251 +3928,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>2774100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5593400</v>
+      </c>
+      <c r="F35" s="3">
         <v>979700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>778200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1363200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>204200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1975400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>698200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2453300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1570600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1797000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1695400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2511100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>513400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1737100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1207700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1005700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>829300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1325600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1201900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1635500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1512500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2082100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1876800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-689800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-260300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1060700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1806300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>1578300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-125200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1588200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1958100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>2221000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>974000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>5155100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>1573000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>1874300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>851200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>1497400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>1570800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4064,8 +4232,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4107,1079 +4277,1135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>32584500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>31865800</v>
+      </c>
+      <c r="F41" s="3">
         <v>30911300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>31321700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>27820000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>30242800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>31554700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>32264100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30940400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>32756400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>30651600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>29729900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>28242200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>28608300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>25525100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>25107500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>24467000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>24401500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>18483400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>18885000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>18400400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>19554400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>21061200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>23100000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>22244200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>23543400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>22245000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>21458300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>21903300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>23968500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>20712000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>20910700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>19699000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>20398700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>19982800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>19958700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>18255500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>18680000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>15966100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>14899000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1264800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1867700</v>
+      </c>
+      <c r="F42" s="3">
         <v>1199300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1399000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1098900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1392200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1676100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2409700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1198700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1517900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1077600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1183700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1599400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1985100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2717400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1682500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>2533400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1445800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2798500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1378900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>2020900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>2093700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>2581100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>661000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1509000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1674400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>2312200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1683700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1391400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1569100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>2163500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1971800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>2351100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>1927100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>2024600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>850800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>1342400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>1325400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>1798800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>741500</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>7045800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7990200</v>
+      </c>
+      <c r="F43" s="3">
         <v>7360100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6730200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6672900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>7752000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6526400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6798200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7108900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8198700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8236300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>7233300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>6682900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7975900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>18722500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>17828900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>18033200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>17203400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>16003700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>16281300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>17464900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>18409000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>17037000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>18269900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>19568500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>22133100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>22986000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>23210000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>24404300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>26378300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>24184900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>24528000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>23800900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>23876100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>23548200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>23598100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>23382900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>23443100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>23391900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>21069000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>15688700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>15918800</v>
+      </c>
+      <c r="F44" s="3">
         <v>15468900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>16470600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>16380400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>16498300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>15949600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>17215800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>16632500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>16151300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>16597700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>15773500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>15812400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>16302700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>14992300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>14451700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>14108300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>12739200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>12362000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>12698600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>12760300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>10958300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>10618500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>11759300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>14089000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>13748600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>14270100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>14972300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>14280800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>15249000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>15280300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>14902300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>13833300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>13772000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>13521800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>12893200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>13062500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>12099800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>12294300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>11016100</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>5717800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5358800</v>
+      </c>
+      <c r="F45" s="3">
         <v>5322400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5929800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3915700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3761300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3817700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3864900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3228900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2953700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3538500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2672400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2697600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2892400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2582600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2781500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3211300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2917100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2528700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2365200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2785900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2720400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2647800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2448500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2856900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3222400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>3325500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>3050000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>3206600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>3442600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>3540300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>3376700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>3186800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>2630700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>3003500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>2940400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>2874900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>2598600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>2745700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>2549900</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>81534100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>82228600</v>
+      </c>
+      <c r="F46" s="3">
         <v>78940200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>80914600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>75033600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>78049500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>77627300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>80398000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>76369400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>78493700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>76276000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>71625500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>69611800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>72053400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>64539900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>61852200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>62353200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>58707100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>52176400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>51609000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>53432500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>53735800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>53945600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>56238600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>60267500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>64321900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>65138900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>64374400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>65186300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>70607500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>65881100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>65689500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>62871000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>62604600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>62080800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>60241200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>58918300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>58147000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>56196900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>50275500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>13980300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>14714200</v>
+      </c>
+      <c r="F47" s="3">
         <v>15588800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>15512900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>15040100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>14130900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>13529600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>14794800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>14106100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>14380400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>14328400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>13589700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>13685900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>13322500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>39947700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>38842300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>39957400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>36702200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>36697700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>39334800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>39898500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>36438600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>34974300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>36072700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>37591000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>38587900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>41309700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>42379100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>41723100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>44050400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>42706700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>43589900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>40141400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>38270300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>39752500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>39447300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>37564700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>35768200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>36278700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>32914600</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>22840100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>20102400</v>
+      </c>
+      <c r="F48" s="3">
         <v>20971700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>21104900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>21900000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>21435500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>20323500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>21350700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20480900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>21383800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>21717300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>21624800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>22458800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>23832200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>56759800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>54883300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>57722300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>54703900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>55283900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>57766500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>58842200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>56304700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>55156600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>58885100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>64648300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>67641100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>70396900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>69840800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>69080700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>71408900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>68937400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>69306200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>66371900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>64641100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>67313500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>67371400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>66201300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>64795700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>65336300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>57889000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>4814700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1866100</v>
+      </c>
+      <c r="F49" s="3">
         <v>6595200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7061900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7355600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1902400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6752300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>7042100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>6487800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1788400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>6627700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6173700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>6326500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1523600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>6177800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>5549300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>5896900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>5640700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5651100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5957100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>6023200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5805000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>5920700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>6159200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>6588800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6699400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>6843300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>7153800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>6906900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>7153400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>7027600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>6948800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>6638400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>6703300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>6777900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>6845000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>6917500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>6902600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>7072200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>7100000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5297,8 +5523,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5416,127 +5648,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>3231800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3413000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3335500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3690100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3696900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3817000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3304600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3407400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3263400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3319400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3646000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3526600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3477600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3417900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3987200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3654900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3612700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3427900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3047000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3262300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3377400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3136000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2321700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2317300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2457500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3015200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2963400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3001800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>3112400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3007600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2842500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2752800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2612100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2697200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>2718800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>2619900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>2558700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>2545100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>2509000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>2508500</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5654,127 +5898,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>211867300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>210743600</v>
+      </c>
+      <c r="F54" s="3">
         <v>209515700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>212794300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>207065300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>205517700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>199555700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>204335200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>194646300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>196847400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>194589700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>185298800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>183098900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>185581300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>171412400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>164782000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>169542500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>159181700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>152856000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>157929800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>161573800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>155420100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>152318900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>159673000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>171553100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>180265500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>186652100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>186749900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>186009400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>196227800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>187395300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>188287300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>178634900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>174916400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>178643600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>176524800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>172160600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>168158600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>167393000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>150687500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5816,8 +6072,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5859,722 +6117,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>10106000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11204700</v>
+      </c>
+      <c r="F57" s="3">
         <v>10055200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10272800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9544300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11108600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9105900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9844600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9166400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>10643200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>9834400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9595400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9379400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>10729600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8229500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>8262600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>7906400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>8208600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>7103200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>6214100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7507200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7714400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7030500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>7647300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>6668500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>8444100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>8190300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>9350700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>9661500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>11386700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>9974200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>10246200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>9979600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>11070600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>9783200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>9918400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>9848600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>10496300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>8840000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>8735600</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>33021800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>31966900</v>
+      </c>
+      <c r="F58" s="3">
         <v>31529700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>30214300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>31880100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>30516700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>30489700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>29508900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>30394100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>27665900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>26806900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>25144600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>24567100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>25279400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>23322400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>22488700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>22055100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>20705500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>21320900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>22029000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>24005600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>21309900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>24361000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>24289000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>28445400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>28618900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>28784900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>30135600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>29217900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>31921500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>30886700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>30923300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>28747700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>27415300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>28327700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>26855000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>26687500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>25782500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>27889600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>23506900</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>14140200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>14737500</v>
+      </c>
+      <c r="F59" s="3">
         <v>12064200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>12470000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12052700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11038100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12634000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12790300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12482300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12500300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12666500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11726000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>11576700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>10875500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>12258400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>12299700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>12484500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10955100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>9485500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>9885000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>10818500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>11498400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>10577800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>11458500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12230300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>13947700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>13246200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>12275300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>12679800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>14170400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>12582900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>12657300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>12284500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>12355900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>11474200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>12384200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>11706700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>11875000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>11237200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>11497900</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>63232700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>64177100</v>
+      </c>
+      <c r="F60" s="3">
         <v>58002200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>57248000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>57874200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>57531000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>56070800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>56200300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>55745200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>55029500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>52669500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>49482800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>48328900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>50040800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>43810300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>43051000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>42446100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>39869200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>37909600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>38128100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>42331400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>40522600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>41969200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>43394700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>47344200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>51010700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>50221500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>51761600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>51559200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>57478600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>53443700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>53826800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>51011800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>50841900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>49585100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>49157600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>48242900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>48153800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>47966900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>43740400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>55422400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>54865700</v>
+      </c>
+      <c r="F61" s="3">
         <v>54872300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>57065100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>50410700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>48110000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>44970700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>45788600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>40266100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>41726600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>40372900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>37245200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>35915600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>34758900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>31029200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>30424300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>33817000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>33095400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>30820600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>33761600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>32731700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>33431900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>31560400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>35223500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>36754100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>37189000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>38056300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>40158500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>40971400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>40419900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>38327200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>38890400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>37015300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>35633500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>37745500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>37919600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>36787600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>36095900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>34934500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>31369500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>9216100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6798800</v>
+      </c>
+      <c r="F62" s="3">
         <v>7876400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>8541400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>8561900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>6628800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5988200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>6339100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5868000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4544300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6007900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5444900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5132800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3921600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>15611200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>15315400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>15846100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>14687400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>15176300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>15728600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>15919700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>15012200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>15926800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>16444700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>18047000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>19065900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>18714200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>15702100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>15512100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>16012000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>14716400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>15224100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>14551800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>14004900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>14924200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>17377700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>17247000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>16766300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>17244300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>15224100</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6692,8 +6988,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6811,8 +7113,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6930,127 +7238,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>134174500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>134343000</v>
+      </c>
+      <c r="F66" s="3">
         <v>128014200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>130089600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>123456100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>121190600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>114508500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>115879200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>109496700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>110861000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>107086400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>100418000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>98054900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>99055000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>92595600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>90712300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>94036300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>89642200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>85730200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>89392700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>93032200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>91026600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>91431500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>97022300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>104300500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>109677500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>109570300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>110095900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>110466500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>116775000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>109170400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>110594600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>105027400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>103197300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>104957800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>106975800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>104614600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>103449300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>102608900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>92460100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7092,8 +7412,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7211,8 +7533,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7330,8 +7658,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7449,8 +7783,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7568,127 +7908,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>60343900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>58966600</v>
+      </c>
+      <c r="F72" s="3">
         <v>72029600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>76169100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>77294500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>74272700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>70338800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>76564800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>67450000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>70372600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>75257000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>70278200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>70849000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>75075800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>70350800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>62309300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>64549200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>63339800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>63856600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>66311200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>66373500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>63110000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>62211300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>64155600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>68357000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>71739400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>75729600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>75749200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>74166900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>76626700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>75791000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>73472500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>70546500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>68806400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>67905100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>63356500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>62171600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>59543400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>58655500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>57510200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7806,8 +8158,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7925,8 +8283,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8044,127 +8408,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>76049500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>74321600</v>
+      </c>
+      <c r="F76" s="3">
         <v>79506500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>80801700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>81765800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>82315100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>83117500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>86493800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>83368600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>83944300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>85521100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>82779900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>82979100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>84133900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>78816800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>74069700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>75506300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>69539600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>67125800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>68537100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>68541700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>64393500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>60887400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>62650700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>67252600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>70588000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>77081800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>76654000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>75542900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>79452800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>78224900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>77692700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>73607500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>71719200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>73685900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>69549000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>67545900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>64709300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>64784100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>58227400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8282,251 +8658,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>2774100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5593400</v>
+      </c>
+      <c r="F81" s="3">
         <v>979700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>778200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1363200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>204200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1975400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>698200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2453300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1570600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1797000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1695400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2511100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>513400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1737100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1207700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1005700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>829300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1325600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1201900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1635500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1512500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2082100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1876800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-689800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-260300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1060700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1806300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>1578300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-125200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1588200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1958100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>2221000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>974000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>5155100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>1573000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>1874300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>851200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>1497400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>1570800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8568,127 +8962,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5747600</v>
+      </c>
+      <c r="F83" s="3">
         <v>1152300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1248600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1168200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>-254900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1628800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1259200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1284300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-176800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1361800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1353800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1188000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>7077700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1275100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1249700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1088000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1016400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1030500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1129800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1112000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1274000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1101400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1128500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1274500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1499000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1838600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1451000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>1557300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1953800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1568100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>1537000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>1698200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>1644000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>1621900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>1571500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>1608900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>1617300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>1453900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>1428200</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8806,8 +9208,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8925,8 +9333,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9044,8 +9458,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9163,8 +9583,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9282,127 +9708,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1799600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2877400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1989200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1893400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>593700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>927100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>538300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1046700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-505200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2152400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>296300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1230800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1356400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3131400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2637100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4614100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>4166200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4859300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>4463600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2096900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>53300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1745500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2377100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>4468800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-612200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>3295100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1780500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1970000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1791600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2665100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>957800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1697800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>1949300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>3299800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1189200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>2842800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1596800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>3785700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>586600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>1958100</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9444,127 +9882,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-3566500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1430300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-962800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-712900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-888400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1225600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-669300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-581100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-862800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-790500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-622200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-483400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-478700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-664200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-181600000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-190171000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-135691000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-123889000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-102949000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-101052000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-590300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-647000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-625100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-450100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-717300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1050200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-889500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-514100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-892300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-1001200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-866600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-742000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-1317100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-877800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-744800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-1006800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-1127200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-1226300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-1772000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-1140500</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9682,8 +10128,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9801,127 +10253,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2455000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1990400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1141400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-990900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1456100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2038000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-748400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2279100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1197300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2154300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1789800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1088200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-875500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-702400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1107900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-959300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1875600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>38000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1065300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-706500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-946100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-944400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2642000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1510700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-932500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1616600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-550300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1906300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1540200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-782100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1126000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-1234800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-2217700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-1661600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-1108800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-1174000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-1616300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-1052200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-1697200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-1407000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9963,127 +10427,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>839300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>870200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>1025500</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>1013800</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>1171300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>1007000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>691000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-725800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-749900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-653500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-685500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-318400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-240600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-148000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-412500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-431100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-449000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-453000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-451500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-473700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-465300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-443000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-436400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-401900</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-391000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-391000</v>
       </c>
       <c r="AL96" s="3">
         <v>-391000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-391000</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>-391000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-383700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-351700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-351700</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10201,8 +10673,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10320,8 +10798,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10439,361 +10923,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>1540700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-59600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-809100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2868700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2253400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-790300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>516600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1644900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>509400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2750100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1841800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1726100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-102100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1125000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2598900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2191000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4107000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>507400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-3293800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-517600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1035600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-2591300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-312400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>95300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>954500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>993100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-600400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-463100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-767900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>741400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>91500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-33100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-548600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-397500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-144300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-233700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-800500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>233300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>604900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-281900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-454000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-985200</v>
+      </c>
+      <c r="F101" s="3">
         <v>1848100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2890300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1334100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1285300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1029600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>522400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>1560400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>260100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1437700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>523900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>1653500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>1404200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1346100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>483600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>1514500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1132200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>384500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-37700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>57300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>973000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-97400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-267900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>39200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-640600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>343600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-117200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-426400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>259100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-459500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>348400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>4500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-824900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>88000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>268100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>37500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-252800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>1572800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-207900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1412600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1424400</v>
+      </c>
+      <c r="F102" s="3">
         <v>1365500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4487700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3569800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2886400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2154500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2477800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>141100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>4033500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-681300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2391000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1939200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1564100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2415900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1947300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-302000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>6536900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>489000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>835100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1871100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-817300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-674700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>2785500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-551000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2031000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>973500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-516700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-942900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>2883500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-536200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>778300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-812500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>415900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>24000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>1703200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-782500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>2713900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>1067100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>61200</v>
       </c>
     </row>
